--- a/artfynd/A 61429-2022 artfynd.xlsx
+++ b/artfynd/A 61429-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61429-2022 artfynd.xlsx
+++ b/artfynd/A 61429-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,274 +1176,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112849046</v>
-      </c>
-      <c r="B6" t="n">
-        <v>104191</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>340</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Motorpet, SV om, S om skogsväg, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>543198</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6361121</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Hultsfred</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Gårdveda</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Hf-Hul-1054</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>23 skott varav 1 blommade.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tallmo.</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112845113</v>
-      </c>
-      <c r="B7" t="n">
-        <v>96145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221940</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mellanlummer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lycopodium zeilleri</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Slätmon, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>543133</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6361110</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Hultsfred</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Gårdveda</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Hf-Hul-1696</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 675 skott varav minst 180 är sporbärande.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gles tallskog.</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Gunnel Gustafson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
